--- a/Team-Data/2008-09/2-2-2008-09.xlsx
+++ b/Team-Data/2008-09/2-2-2008-09.xlsx
@@ -50,7 +50,6 @@
       <right style="thin"/>
       <top style="thin"/>
       <bottom style="thin"/>
-      <diagonal/>
     </border>
   </borders>
   <cellStyleXfs count="1">
@@ -66,6 +65,74 @@
     <cellStyle name="Normal" xfId="0" builtinId="0" hidden="0"/>
   </cellStyles>
   <tableStyles count="0" defaultTableStyle="TableStyleMedium9" defaultPivotStyle="PivotStyleLight16"/>
+  <colors>
+    <indexedColors>
+      <rgbColor rgb="00000000"/>
+      <rgbColor rgb="00FFFFFF"/>
+      <rgbColor rgb="00FF0000"/>
+      <rgbColor rgb="0000FF00"/>
+      <rgbColor rgb="000000FF"/>
+      <rgbColor rgb="00FFFF00"/>
+      <rgbColor rgb="00FF00FF"/>
+      <rgbColor rgb="0000FFFF"/>
+      <rgbColor rgb="00000000"/>
+      <rgbColor rgb="00FFFFFF"/>
+      <rgbColor rgb="00FF0000"/>
+      <rgbColor rgb="0000FF00"/>
+      <rgbColor rgb="000000FF"/>
+      <rgbColor rgb="00FFFF00"/>
+      <rgbColor rgb="00FF00FF"/>
+      <rgbColor rgb="0000FFFF"/>
+      <rgbColor rgb="00800000"/>
+      <rgbColor rgb="00008000"/>
+      <rgbColor rgb="00000080"/>
+      <rgbColor rgb="00808000"/>
+      <rgbColor rgb="00800080"/>
+      <rgbColor rgb="00008080"/>
+      <rgbColor rgb="00C0C0C0"/>
+      <rgbColor rgb="00808080"/>
+      <rgbColor rgb="009999FF"/>
+      <rgbColor rgb="00993366"/>
+      <rgbColor rgb="00FFFFCC"/>
+      <rgbColor rgb="00CCFFFF"/>
+      <rgbColor rgb="00660066"/>
+      <rgbColor rgb="00FF8080"/>
+      <rgbColor rgb="000066CC"/>
+      <rgbColor rgb="00CCCCFF"/>
+      <rgbColor rgb="00000080"/>
+      <rgbColor rgb="00FF00FF"/>
+      <rgbColor rgb="00FFFF00"/>
+      <rgbColor rgb="0000FFFF"/>
+      <rgbColor rgb="00800080"/>
+      <rgbColor rgb="00800000"/>
+      <rgbColor rgb="00008080"/>
+      <rgbColor rgb="000000FF"/>
+      <rgbColor rgb="0000CCFF"/>
+      <rgbColor rgb="00CCFFFF"/>
+      <rgbColor rgb="00CCFFCC"/>
+      <rgbColor rgb="00FFFF99"/>
+      <rgbColor rgb="0099CCFF"/>
+      <rgbColor rgb="00FF99CC"/>
+      <rgbColor rgb="00CC99FF"/>
+      <rgbColor rgb="00FFCC99"/>
+      <rgbColor rgb="003366FF"/>
+      <rgbColor rgb="0033CCCC"/>
+      <rgbColor rgb="0099CC00"/>
+      <rgbColor rgb="00FFCC00"/>
+      <rgbColor rgb="00FF9900"/>
+      <rgbColor rgb="00FF6600"/>
+      <rgbColor rgb="00666699"/>
+      <rgbColor rgb="00969696"/>
+      <rgbColor rgb="00003366"/>
+      <rgbColor rgb="00339966"/>
+      <rgbColor rgb="00003300"/>
+      <rgbColor rgb="00333300"/>
+      <rgbColor rgb="00993300"/>
+      <rgbColor rgb="00993366"/>
+      <rgbColor rgb="00333399"/>
+      <rgbColor rgb="00333333"/>
+    </indexedColors>
+  </colors>
 </styleSheet>
 </file>
 
@@ -739,10 +806,10 @@
         <v>1.7</v>
       </c>
       <c r="AD2" t="n">
-        <v>14</v>
+        <v>12</v>
       </c>
       <c r="AE2" t="n">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="AF2" t="n">
         <v>11</v>
@@ -751,7 +818,7 @@
         <v>11</v>
       </c>
       <c r="AH2" t="n">
-        <v>26</v>
+        <v>28</v>
       </c>
       <c r="AI2" t="n">
         <v>23</v>
@@ -760,10 +827,10 @@
         <v>19</v>
       </c>
       <c r="AK2" t="n">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="AL2" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="AM2" t="n">
         <v>3</v>
@@ -775,7 +842,7 @@
         <v>18</v>
       </c>
       <c r="AP2" t="n">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="AQ2" t="n">
         <v>28</v>
@@ -787,19 +854,19 @@
         <v>19</v>
       </c>
       <c r="AT2" t="n">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="AU2" t="n">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="AV2" t="n">
         <v>7</v>
       </c>
       <c r="AW2" t="n">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="AX2" t="n">
-        <v>19</v>
+        <v>18</v>
       </c>
       <c r="AY2" t="n">
         <v>12</v>
@@ -808,10 +875,10 @@
         <v>9</v>
       </c>
       <c r="BA2" t="n">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="BB2" t="n">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="BC2" t="n">
         <v>11</v>
@@ -826,7 +893,7 @@
       </c>
       <c r="BF2" t="inlineStr">
         <is>
-          <t>2-2-2008-09</t>
+          <t>2009-02-02</t>
         </is>
       </c>
     </row>
@@ -843,22 +910,22 @@
         </is>
       </c>
       <c r="D3" t="n">
-        <v>48</v>
+        <v>49</v>
       </c>
       <c r="E3" t="n">
-        <v>39</v>
+        <v>40</v>
       </c>
       <c r="F3" t="n">
         <v>9</v>
       </c>
       <c r="G3" t="n">
-        <v>0.8129999999999999</v>
+        <v>0.8159999999999999</v>
       </c>
       <c r="H3" t="n">
         <v>48.4</v>
       </c>
       <c r="I3" t="n">
-        <v>37.2</v>
+        <v>37.1</v>
       </c>
       <c r="J3" t="n">
         <v>77</v>
@@ -867,73 +934,73 @@
         <v>0.483</v>
       </c>
       <c r="L3" t="n">
-        <v>6.7</v>
+        <v>6.6</v>
       </c>
       <c r="M3" t="n">
         <v>17</v>
       </c>
       <c r="N3" t="n">
-        <v>0.392</v>
+        <v>0.389</v>
       </c>
       <c r="O3" t="n">
         <v>20.4</v>
       </c>
       <c r="P3" t="n">
-        <v>26.4</v>
+        <v>26.5</v>
       </c>
       <c r="Q3" t="n">
-        <v>0.775</v>
+        <v>0.771</v>
       </c>
       <c r="R3" t="n">
         <v>10.9</v>
       </c>
       <c r="S3" t="n">
-        <v>31.8</v>
+        <v>31.7</v>
       </c>
       <c r="T3" t="n">
-        <v>42.8</v>
+        <v>42.6</v>
       </c>
       <c r="U3" t="n">
-        <v>22.8</v>
+        <v>22.7</v>
       </c>
       <c r="V3" t="n">
         <v>15.7</v>
       </c>
       <c r="W3" t="n">
-        <v>8.5</v>
+        <v>8.6</v>
       </c>
       <c r="X3" t="n">
-        <v>4.9</v>
+        <v>4.8</v>
       </c>
       <c r="Y3" t="n">
-        <v>4.7</v>
+        <v>4.6</v>
       </c>
       <c r="Z3" t="n">
-        <v>23</v>
+        <v>23.1</v>
       </c>
       <c r="AA3" t="n">
-        <v>22.8</v>
+        <v>22.9</v>
       </c>
       <c r="AB3" t="n">
-        <v>101.6</v>
+        <v>101.3</v>
       </c>
       <c r="AC3" t="n">
-        <v>10.1</v>
+        <v>10</v>
       </c>
       <c r="AD3" t="n">
-        <v>6</v>
+        <v>2</v>
       </c>
       <c r="AE3" t="n">
         <v>1</v>
       </c>
       <c r="AF3" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="AG3" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="AH3" t="n">
-        <v>12</v>
+        <v>14</v>
       </c>
       <c r="AI3" t="n">
         <v>10</v>
@@ -945,13 +1012,13 @@
         <v>2</v>
       </c>
       <c r="AL3" t="n">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="AM3" t="n">
         <v>18</v>
       </c>
       <c r="AN3" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="AO3" t="n">
         <v>7</v>
@@ -960,37 +1027,37 @@
         <v>7</v>
       </c>
       <c r="AQ3" t="n">
-        <v>10</v>
+        <v>13</v>
       </c>
       <c r="AR3" t="n">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="AS3" t="n">
+        <v>6</v>
+      </c>
+      <c r="AT3" t="n">
+        <v>8</v>
+      </c>
+      <c r="AU3" t="n">
         <v>5</v>
       </c>
-      <c r="AT3" t="n">
-        <v>6</v>
-      </c>
-      <c r="AU3" t="n">
-        <v>4</v>
-      </c>
       <c r="AV3" t="n">
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="AW3" t="n">
         <v>3</v>
       </c>
       <c r="AX3" t="n">
+        <v>15</v>
+      </c>
+      <c r="AY3" t="n">
         <v>13</v>
-      </c>
-      <c r="AY3" t="n">
-        <v>14</v>
       </c>
       <c r="AZ3" t="n">
         <v>26</v>
       </c>
       <c r="BA3" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="BB3" t="n">
         <v>9</v>
@@ -1008,7 +1075,7 @@
       </c>
       <c r="BF3" t="inlineStr">
         <is>
-          <t>2-2-2008-09</t>
+          <t>2009-02-02</t>
         </is>
       </c>
     </row>
@@ -1025,16 +1092,16 @@
         </is>
       </c>
       <c r="D4" t="n">
-        <v>48</v>
+        <v>47</v>
       </c>
       <c r="E4" t="n">
         <v>19</v>
       </c>
       <c r="F4" t="n">
-        <v>29</v>
+        <v>28</v>
       </c>
       <c r="G4" t="n">
-        <v>0.396</v>
+        <v>0.404</v>
       </c>
       <c r="H4" t="n">
         <v>48.7</v>
@@ -1043,10 +1110,10 @@
         <v>34</v>
       </c>
       <c r="J4" t="n">
-        <v>76</v>
+        <v>76.2</v>
       </c>
       <c r="K4" t="n">
-        <v>0.448</v>
+        <v>0.447</v>
       </c>
       <c r="L4" t="n">
         <v>5.5</v>
@@ -1055,55 +1122,55 @@
         <v>15.4</v>
       </c>
       <c r="N4" t="n">
-        <v>0.359</v>
+        <v>0.358</v>
       </c>
       <c r="O4" t="n">
-        <v>18.3</v>
+        <v>18.4</v>
       </c>
       <c r="P4" t="n">
-        <v>24.6</v>
+        <v>24.7</v>
       </c>
       <c r="Q4" t="n">
-        <v>0.741</v>
+        <v>0.744</v>
       </c>
       <c r="R4" t="n">
         <v>10.6</v>
       </c>
       <c r="S4" t="n">
-        <v>28.4</v>
+        <v>28.5</v>
       </c>
       <c r="T4" t="n">
-        <v>39</v>
+        <v>39.1</v>
       </c>
       <c r="U4" t="n">
         <v>20.5</v>
       </c>
       <c r="V4" t="n">
-        <v>15.7</v>
+        <v>15.5</v>
       </c>
       <c r="W4" t="n">
         <v>7.1</v>
       </c>
       <c r="X4" t="n">
-        <v>4.7</v>
+        <v>4.6</v>
       </c>
       <c r="Y4" t="n">
-        <v>6</v>
+        <v>6.1</v>
       </c>
       <c r="Z4" t="n">
-        <v>22.4</v>
+        <v>22.2</v>
       </c>
       <c r="AA4" t="n">
-        <v>21.3</v>
+        <v>21.4</v>
       </c>
       <c r="AB4" t="n">
-        <v>91.8</v>
+        <v>92</v>
       </c>
       <c r="AC4" t="n">
-        <v>-2.4</v>
+        <v>-2</v>
       </c>
       <c r="AD4" t="n">
-        <v>6</v>
+        <v>12</v>
       </c>
       <c r="AE4" t="n">
         <v>21</v>
@@ -1115,7 +1182,7 @@
         <v>21</v>
       </c>
       <c r="AH4" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="AI4" t="n">
         <v>30</v>
@@ -1124,7 +1191,7 @@
         <v>30</v>
       </c>
       <c r="AK4" t="n">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="AL4" t="n">
         <v>24</v>
@@ -1133,22 +1200,22 @@
         <v>25</v>
       </c>
       <c r="AN4" t="n">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="AO4" t="n">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="AP4" t="n">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="AQ4" t="n">
-        <v>27</v>
+        <v>26</v>
       </c>
       <c r="AR4" t="n">
         <v>19</v>
       </c>
       <c r="AS4" t="n">
-        <v>27</v>
+        <v>26</v>
       </c>
       <c r="AT4" t="n">
         <v>26</v>
@@ -1157,13 +1224,13 @@
         <v>16</v>
       </c>
       <c r="AV4" t="n">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="AW4" t="n">
         <v>16</v>
       </c>
       <c r="AX4" t="n">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="AY4" t="n">
         <v>29</v>
@@ -1172,13 +1239,13 @@
         <v>23</v>
       </c>
       <c r="BA4" t="n">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="BB4" t="n">
         <v>30</v>
       </c>
       <c r="BC4" t="n">
-        <v>20</v>
+        <v>18</v>
       </c>
       <c r="BD4" t="n">
         <v>10</v>
@@ -1190,7 +1257,7 @@
       </c>
       <c r="BF4" t="inlineStr">
         <is>
-          <t>2-2-2008-09</t>
+          <t>2009-02-02</t>
         </is>
       </c>
     </row>
@@ -1207,16 +1274,16 @@
         </is>
       </c>
       <c r="D5" t="n">
-        <v>47</v>
+        <v>48</v>
       </c>
       <c r="E5" t="n">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="F5" t="n">
         <v>27</v>
       </c>
       <c r="G5" t="n">
-        <v>0.426</v>
+        <v>0.438</v>
       </c>
       <c r="H5" t="n">
         <v>48.6</v>
@@ -1225,76 +1292,76 @@
         <v>37.6</v>
       </c>
       <c r="J5" t="n">
-        <v>84.09999999999999</v>
+        <v>83.8</v>
       </c>
       <c r="K5" t="n">
-        <v>0.447</v>
+        <v>0.448</v>
       </c>
       <c r="L5" t="n">
         <v>6</v>
       </c>
       <c r="M5" t="n">
-        <v>16.2</v>
+        <v>16.1</v>
       </c>
       <c r="N5" t="n">
         <v>0.374</v>
       </c>
       <c r="O5" t="n">
-        <v>18.4</v>
+        <v>18.7</v>
       </c>
       <c r="P5" t="n">
-        <v>23.2</v>
+        <v>23.7</v>
       </c>
       <c r="Q5" t="n">
-        <v>0.79</v>
+        <v>0.789</v>
       </c>
       <c r="R5" t="n">
-        <v>11.9</v>
+        <v>12</v>
       </c>
       <c r="S5" t="n">
-        <v>30.4</v>
+        <v>30.3</v>
       </c>
       <c r="T5" t="n">
         <v>42.3</v>
       </c>
       <c r="U5" t="n">
-        <v>21</v>
+        <v>21.1</v>
       </c>
       <c r="V5" t="n">
-        <v>15</v>
+        <v>15.1</v>
       </c>
       <c r="W5" t="n">
         <v>7.4</v>
       </c>
       <c r="X5" t="n">
-        <v>5.7</v>
+        <v>5.8</v>
       </c>
       <c r="Y5" t="n">
         <v>5.4</v>
       </c>
       <c r="Z5" t="n">
-        <v>22.2</v>
+        <v>22.1</v>
       </c>
       <c r="AA5" t="n">
-        <v>20.1</v>
+        <v>20.3</v>
       </c>
       <c r="AB5" t="n">
-        <v>99.7</v>
+        <v>99.90000000000001</v>
       </c>
       <c r="AC5" t="n">
-        <v>-2.5</v>
+        <v>-2.2</v>
       </c>
       <c r="AD5" t="n">
-        <v>14</v>
+        <v>5</v>
       </c>
       <c r="AE5" t="n">
-        <v>20</v>
+        <v>18</v>
       </c>
       <c r="AF5" t="n">
+        <v>18</v>
+      </c>
+      <c r="AG5" t="n">
         <v>19</v>
-      </c>
-      <c r="AG5" t="n">
-        <v>20</v>
       </c>
       <c r="AH5" t="n">
         <v>5</v>
@@ -1303,10 +1370,10 @@
         <v>8</v>
       </c>
       <c r="AJ5" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="AK5" t="n">
-        <v>23</v>
+        <v>19</v>
       </c>
       <c r="AL5" t="n">
         <v>20</v>
@@ -1315,19 +1382,19 @@
         <v>22</v>
       </c>
       <c r="AN5" t="n">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="AO5" t="n">
         <v>20</v>
       </c>
       <c r="AP5" t="n">
-        <v>22</v>
+        <v>20</v>
       </c>
       <c r="AQ5" t="n">
         <v>8</v>
       </c>
       <c r="AR5" t="n">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="AS5" t="n">
         <v>13</v>
@@ -1339,7 +1406,7 @@
         <v>13</v>
       </c>
       <c r="AV5" t="n">
-        <v>18</v>
+        <v>21</v>
       </c>
       <c r="AW5" t="n">
         <v>13</v>
@@ -1348,19 +1415,19 @@
         <v>4</v>
       </c>
       <c r="AY5" t="n">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="AZ5" t="n">
         <v>22</v>
       </c>
       <c r="BA5" t="n">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="BB5" t="n">
         <v>12</v>
       </c>
       <c r="BC5" t="n">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="BD5" t="n">
         <v>10</v>
@@ -1372,7 +1439,7 @@
       </c>
       <c r="BF5" t="inlineStr">
         <is>
-          <t>2-2-2008-09</t>
+          <t>2009-02-02</t>
         </is>
       </c>
     </row>
@@ -1389,85 +1456,85 @@
         </is>
       </c>
       <c r="D6" t="n">
-        <v>45</v>
+        <v>46</v>
       </c>
       <c r="E6" t="n">
         <v>37</v>
       </c>
       <c r="F6" t="n">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="G6" t="n">
-        <v>0.822</v>
+        <v>0.804</v>
       </c>
       <c r="H6" t="n">
         <v>48.1</v>
       </c>
       <c r="I6" t="n">
-        <v>37.4</v>
+        <v>37.2</v>
       </c>
       <c r="J6" t="n">
-        <v>78.40000000000001</v>
+        <v>78.2</v>
       </c>
       <c r="K6" t="n">
-        <v>0.477</v>
+        <v>0.476</v>
       </c>
       <c r="L6" t="n">
-        <v>7.9</v>
+        <v>7.8</v>
       </c>
       <c r="M6" t="n">
-        <v>20.7</v>
+        <v>20.6</v>
       </c>
       <c r="N6" t="n">
-        <v>0.38</v>
+        <v>0.378</v>
       </c>
       <c r="O6" t="n">
-        <v>18.6</v>
+        <v>18.7</v>
       </c>
       <c r="P6" t="n">
-        <v>24.8</v>
+        <v>25</v>
       </c>
       <c r="Q6" t="n">
-        <v>0.752</v>
+        <v>0.751</v>
       </c>
       <c r="R6" t="n">
         <v>10.7</v>
       </c>
       <c r="S6" t="n">
-        <v>31.1</v>
+        <v>31.2</v>
       </c>
       <c r="T6" t="n">
         <v>41.8</v>
       </c>
       <c r="U6" t="n">
-        <v>20.5</v>
+        <v>20.4</v>
       </c>
       <c r="V6" t="n">
-        <v>12.8</v>
+        <v>13</v>
       </c>
       <c r="W6" t="n">
         <v>7.7</v>
       </c>
       <c r="X6" t="n">
-        <v>5.7</v>
+        <v>5.6</v>
       </c>
       <c r="Y6" t="n">
-        <v>4.1</v>
+        <v>4</v>
       </c>
       <c r="Z6" t="n">
-        <v>20.4</v>
+        <v>20.5</v>
       </c>
       <c r="AA6" t="n">
-        <v>20.6</v>
+        <v>20.7</v>
       </c>
       <c r="AB6" t="n">
-        <v>101.3</v>
+        <v>100.9</v>
       </c>
       <c r="AC6" t="n">
-        <v>10.6</v>
+        <v>10.3</v>
       </c>
       <c r="AD6" t="n">
-        <v>29</v>
+        <v>17</v>
       </c>
       <c r="AE6" t="n">
         <v>2</v>
@@ -1476,7 +1543,7 @@
         <v>1</v>
       </c>
       <c r="AG6" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="AH6" t="n">
         <v>24</v>
@@ -1485,19 +1552,19 @@
         <v>9</v>
       </c>
       <c r="AJ6" t="n">
-        <v>23</v>
+        <v>25</v>
       </c>
       <c r="AK6" t="n">
         <v>4</v>
       </c>
       <c r="AL6" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="AM6" t="n">
-        <v>4</v>
+        <v>6</v>
       </c>
       <c r="AN6" t="n">
-        <v>6</v>
+        <v>8</v>
       </c>
       <c r="AO6" t="n">
         <v>19</v>
@@ -1518,25 +1585,25 @@
         <v>13</v>
       </c>
       <c r="AU6" t="n">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="AV6" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="AW6" t="n">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="AX6" t="n">
         <v>5</v>
       </c>
       <c r="AY6" t="n">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="AZ6" t="n">
-        <v>10</v>
+        <v>12</v>
       </c>
       <c r="BA6" t="n">
-        <v>22</v>
+        <v>20</v>
       </c>
       <c r="BB6" t="n">
         <v>10</v>
@@ -1554,7 +1621,7 @@
       </c>
       <c r="BF6" t="inlineStr">
         <is>
-          <t>2-2-2008-09</t>
+          <t>2009-02-02</t>
         </is>
       </c>
     </row>
@@ -1571,16 +1638,16 @@
         </is>
       </c>
       <c r="D7" t="n">
-        <v>47</v>
+        <v>46</v>
       </c>
       <c r="E7" t="n">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="F7" t="n">
         <v>19</v>
       </c>
       <c r="G7" t="n">
-        <v>0.596</v>
+        <v>0.587</v>
       </c>
       <c r="H7" t="n">
         <v>48.3</v>
@@ -1589,37 +1656,37 @@
         <v>37.9</v>
       </c>
       <c r="J7" t="n">
-        <v>82.90000000000001</v>
+        <v>83.09999999999999</v>
       </c>
       <c r="K7" t="n">
-        <v>0.458</v>
+        <v>0.456</v>
       </c>
       <c r="L7" t="n">
         <v>6.9</v>
       </c>
       <c r="M7" t="n">
-        <v>20.1</v>
+        <v>20.3</v>
       </c>
       <c r="N7" t="n">
         <v>0.342</v>
       </c>
       <c r="O7" t="n">
-        <v>17.8</v>
+        <v>17.7</v>
       </c>
       <c r="P7" t="n">
-        <v>21.8</v>
+        <v>21.7</v>
       </c>
       <c r="Q7" t="n">
-        <v>0.8169999999999999</v>
+        <v>0.8159999999999999</v>
       </c>
       <c r="R7" t="n">
-        <v>11.3</v>
+        <v>11.5</v>
       </c>
       <c r="S7" t="n">
         <v>32</v>
       </c>
       <c r="T7" t="n">
-        <v>43.3</v>
+        <v>43.4</v>
       </c>
       <c r="U7" t="n">
         <v>21.3</v>
@@ -1631,28 +1698,28 @@
         <v>7</v>
       </c>
       <c r="X7" t="n">
-        <v>5.4</v>
+        <v>5.5</v>
       </c>
       <c r="Y7" t="n">
         <v>4.2</v>
       </c>
       <c r="Z7" t="n">
-        <v>19</v>
+        <v>18.8</v>
       </c>
       <c r="AA7" t="n">
         <v>19.5</v>
       </c>
       <c r="AB7" t="n">
-        <v>100.6</v>
+        <v>100.5</v>
       </c>
       <c r="AC7" t="n">
-        <v>1.5</v>
+        <v>1.3</v>
       </c>
       <c r="AD7" t="n">
-        <v>14</v>
+        <v>17</v>
       </c>
       <c r="AE7" t="n">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="AF7" t="n">
         <v>9</v>
@@ -1661,7 +1728,7 @@
         <v>10</v>
       </c>
       <c r="AH7" t="n">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="AI7" t="n">
         <v>6</v>
@@ -1670,7 +1737,7 @@
         <v>7</v>
       </c>
       <c r="AK7" t="n">
-        <v>12</v>
+        <v>14</v>
       </c>
       <c r="AL7" t="n">
         <v>13</v>
@@ -1700,7 +1767,7 @@
         <v>3</v>
       </c>
       <c r="AU7" t="n">
-        <v>12</v>
+        <v>10</v>
       </c>
       <c r="AV7" t="n">
         <v>8</v>
@@ -1712,10 +1779,10 @@
         <v>9</v>
       </c>
       <c r="AY7" t="n">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="AZ7" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="BA7" t="n">
         <v>27</v>
@@ -1724,7 +1791,7 @@
         <v>11</v>
       </c>
       <c r="BC7" t="n">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="BD7" t="n">
         <v>10</v>
@@ -1736,7 +1803,7 @@
       </c>
       <c r="BF7" t="inlineStr">
         <is>
-          <t>2-2-2008-09</t>
+          <t>2009-02-02</t>
         </is>
       </c>
     </row>
@@ -1831,7 +1898,7 @@
         <v>3.8</v>
       </c>
       <c r="AD8" t="n">
-        <v>14</v>
+        <v>12</v>
       </c>
       <c r="AE8" t="n">
         <v>6</v>
@@ -1849,13 +1916,13 @@
         <v>11</v>
       </c>
       <c r="AJ8" t="n">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="AK8" t="n">
         <v>6</v>
       </c>
       <c r="AL8" t="n">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="AM8" t="n">
         <v>15</v>
@@ -1870,7 +1937,7 @@
         <v>1</v>
       </c>
       <c r="AQ8" t="n">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="AR8" t="n">
         <v>22</v>
@@ -1894,7 +1961,7 @@
         <v>3</v>
       </c>
       <c r="AY8" t="n">
-        <v>27</v>
+        <v>28</v>
       </c>
       <c r="AZ8" t="n">
         <v>25</v>
@@ -1903,7 +1970,7 @@
         <v>1</v>
       </c>
       <c r="BB8" t="n">
-        <v>6</v>
+        <v>4</v>
       </c>
       <c r="BC8" t="n">
         <v>6</v>
@@ -1918,7 +1985,7 @@
       </c>
       <c r="BF8" t="inlineStr">
         <is>
-          <t>2-2-2008-09</t>
+          <t>2009-02-02</t>
         </is>
       </c>
     </row>
@@ -2013,16 +2080,16 @@
         <v>-0.2</v>
       </c>
       <c r="AD9" t="n">
-        <v>23</v>
+        <v>17</v>
       </c>
       <c r="AE9" t="n">
-        <v>15</v>
+        <v>13</v>
       </c>
       <c r="AF9" t="n">
         <v>13</v>
       </c>
       <c r="AG9" t="n">
-        <v>15</v>
+        <v>13</v>
       </c>
       <c r="AH9" t="n">
         <v>15</v>
@@ -2049,7 +2116,7 @@
         <v>28</v>
       </c>
       <c r="AP9" t="n">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="AQ9" t="n">
         <v>25</v>
@@ -2061,10 +2128,10 @@
         <v>17</v>
       </c>
       <c r="AT9" t="n">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="AU9" t="n">
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="AV9" t="n">
         <v>1</v>
@@ -2079,13 +2146,13 @@
         <v>4</v>
       </c>
       <c r="AZ9" t="n">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="BA9" t="n">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="BB9" t="n">
-        <v>29</v>
+        <v>28</v>
       </c>
       <c r="BC9" t="n">
         <v>17</v>
@@ -2100,7 +2167,7 @@
       </c>
       <c r="BF9" t="inlineStr">
         <is>
-          <t>2-2-2008-09</t>
+          <t>2009-02-02</t>
         </is>
       </c>
     </row>
@@ -2117,46 +2184,46 @@
         </is>
       </c>
       <c r="D10" t="n">
-        <v>49</v>
+        <v>48</v>
       </c>
       <c r="E10" t="n">
         <v>15</v>
       </c>
       <c r="F10" t="n">
-        <v>34</v>
+        <v>33</v>
       </c>
       <c r="G10" t="n">
-        <v>0.306</v>
+        <v>0.313</v>
       </c>
       <c r="H10" t="n">
-        <v>48.7</v>
+        <v>48.6</v>
       </c>
       <c r="I10" t="n">
-        <v>38.8</v>
+        <v>38.6</v>
       </c>
       <c r="J10" t="n">
-        <v>86</v>
+        <v>85.8</v>
       </c>
       <c r="K10" t="n">
-        <v>0.451</v>
+        <v>0.45</v>
       </c>
       <c r="L10" t="n">
-        <v>6.4</v>
+        <v>6.5</v>
       </c>
       <c r="M10" t="n">
-        <v>17.8</v>
+        <v>17.9</v>
       </c>
       <c r="N10" t="n">
         <v>0.362</v>
       </c>
       <c r="O10" t="n">
-        <v>22.4</v>
+        <v>22.6</v>
       </c>
       <c r="P10" t="n">
-        <v>29.1</v>
+        <v>29.3</v>
       </c>
       <c r="Q10" t="n">
-        <v>0.77</v>
+        <v>0.772</v>
       </c>
       <c r="R10" t="n">
         <v>12.1</v>
@@ -2171,31 +2238,31 @@
         <v>20.4</v>
       </c>
       <c r="V10" t="n">
-        <v>15</v>
+        <v>14.9</v>
       </c>
       <c r="W10" t="n">
         <v>7.9</v>
       </c>
       <c r="X10" t="n">
-        <v>6.6</v>
+        <v>6.5</v>
       </c>
       <c r="Y10" t="n">
-        <v>5.4</v>
+        <v>5.5</v>
       </c>
       <c r="Z10" t="n">
-        <v>22.1</v>
+        <v>22</v>
       </c>
       <c r="AA10" t="n">
         <v>23.7</v>
       </c>
       <c r="AB10" t="n">
-        <v>106.3</v>
+        <v>106.4</v>
       </c>
       <c r="AC10" t="n">
         <v>-4.8</v>
       </c>
       <c r="AD10" t="n">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="AE10" t="n">
         <v>25</v>
@@ -2207,7 +2274,7 @@
         <v>25</v>
       </c>
       <c r="AH10" t="n">
-        <v>3</v>
+        <v>8</v>
       </c>
       <c r="AI10" t="n">
         <v>3</v>
@@ -2234,7 +2301,7 @@
         <v>2</v>
       </c>
       <c r="AQ10" t="n">
-        <v>13</v>
+        <v>11</v>
       </c>
       <c r="AR10" t="n">
         <v>5</v>
@@ -2246,10 +2313,10 @@
         <v>10</v>
       </c>
       <c r="AU10" t="n">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="AV10" t="n">
-        <v>19</v>
+        <v>17</v>
       </c>
       <c r="AW10" t="n">
         <v>7</v>
@@ -2258,10 +2325,10 @@
         <v>1</v>
       </c>
       <c r="AY10" t="n">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="AZ10" t="n">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="BA10" t="n">
         <v>2</v>
@@ -2282,7 +2349,7 @@
       </c>
       <c r="BF10" t="inlineStr">
         <is>
-          <t>2-2-2008-09</t>
+          <t>2009-02-02</t>
         </is>
       </c>
     </row>
@@ -2377,10 +2444,10 @@
         <v>2.9</v>
       </c>
       <c r="AD11" t="n">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="AE11" t="n">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="AF11" t="n">
         <v>9</v>
@@ -2410,7 +2477,7 @@
         <v>13</v>
       </c>
       <c r="AO11" t="n">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="AP11" t="n">
         <v>19</v>
@@ -2425,10 +2492,10 @@
         <v>3</v>
       </c>
       <c r="AT11" t="n">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="AU11" t="n">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="AV11" t="n">
         <v>14</v>
@@ -2443,7 +2510,7 @@
         <v>26</v>
       </c>
       <c r="AZ11" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="BA11" t="n">
         <v>14</v>
@@ -2452,7 +2519,7 @@
         <v>18</v>
       </c>
       <c r="BC11" t="n">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="BD11" t="n">
         <v>10</v>
@@ -2464,7 +2531,7 @@
       </c>
       <c r="BF11" t="inlineStr">
         <is>
-          <t>2-2-2008-09</t>
+          <t>2009-02-02</t>
         </is>
       </c>
     </row>
@@ -2559,19 +2626,19 @@
         <v>-2.3</v>
       </c>
       <c r="AD12" t="n">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="AE12" t="n">
         <v>21</v>
       </c>
       <c r="AF12" t="n">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="AG12" t="n">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="AH12" t="n">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="AI12" t="n">
         <v>2</v>
@@ -2586,7 +2653,7 @@
         <v>8</v>
       </c>
       <c r="AM12" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="AN12" t="n">
         <v>16</v>
@@ -2610,7 +2677,7 @@
         <v>2</v>
       </c>
       <c r="AU12" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="AV12" t="n">
         <v>23</v>
@@ -2619,7 +2686,7 @@
         <v>22</v>
       </c>
       <c r="AX12" t="n">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="AY12" t="n">
         <v>25</v>
@@ -2628,13 +2695,13 @@
         <v>29</v>
       </c>
       <c r="BA12" t="n">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="BB12" t="n">
         <v>3</v>
       </c>
       <c r="BC12" t="n">
-        <v>19</v>
+        <v>21</v>
       </c>
       <c r="BD12" t="n">
         <v>10</v>
@@ -2646,7 +2713,7 @@
       </c>
       <c r="BF12" t="inlineStr">
         <is>
-          <t>2-2-2008-09</t>
+          <t>2009-02-02</t>
         </is>
       </c>
     </row>
@@ -2663,16 +2730,16 @@
         </is>
       </c>
       <c r="D13" t="n">
-        <v>48</v>
+        <v>47</v>
       </c>
       <c r="E13" t="n">
         <v>10</v>
       </c>
       <c r="F13" t="n">
-        <v>38</v>
+        <v>37</v>
       </c>
       <c r="G13" t="n">
-        <v>0.208</v>
+        <v>0.213</v>
       </c>
       <c r="H13" t="n">
         <v>48.6</v>
@@ -2690,10 +2757,10 @@
         <v>5.7</v>
       </c>
       <c r="M13" t="n">
-        <v>17.1</v>
+        <v>17</v>
       </c>
       <c r="N13" t="n">
-        <v>0.332</v>
+        <v>0.333</v>
       </c>
       <c r="O13" t="n">
         <v>17.2</v>
@@ -2702,19 +2769,19 @@
         <v>22.8</v>
       </c>
       <c r="Q13" t="n">
-        <v>0.756</v>
+        <v>0.753</v>
       </c>
       <c r="R13" t="n">
-        <v>11.8</v>
+        <v>11.9</v>
       </c>
       <c r="S13" t="n">
-        <v>29.1</v>
+        <v>29.2</v>
       </c>
       <c r="T13" t="n">
-        <v>40.9</v>
+        <v>41.1</v>
       </c>
       <c r="U13" t="n">
-        <v>20.1</v>
+        <v>20</v>
       </c>
       <c r="V13" t="n">
         <v>15</v>
@@ -2723,7 +2790,7 @@
         <v>7</v>
       </c>
       <c r="X13" t="n">
-        <v>6.4</v>
+        <v>6.5</v>
       </c>
       <c r="Y13" t="n">
         <v>5.6</v>
@@ -2735,28 +2802,28 @@
         <v>19.6</v>
       </c>
       <c r="AB13" t="n">
-        <v>93</v>
+        <v>92.90000000000001</v>
       </c>
       <c r="AC13" t="n">
-        <v>-8.4</v>
+        <v>-8.1</v>
       </c>
       <c r="AD13" t="n">
-        <v>6</v>
+        <v>12</v>
       </c>
       <c r="AE13" t="n">
         <v>29</v>
       </c>
       <c r="AF13" t="n">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="AG13" t="n">
         <v>29</v>
       </c>
       <c r="AH13" t="n">
-        <v>6</v>
+        <v>4</v>
       </c>
       <c r="AI13" t="n">
-        <v>27</v>
+        <v>28</v>
       </c>
       <c r="AJ13" t="n">
         <v>8</v>
@@ -2771,40 +2838,40 @@
         <v>17</v>
       </c>
       <c r="AN13" t="n">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="AO13" t="n">
         <v>27</v>
       </c>
       <c r="AP13" t="n">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="AQ13" t="n">
+        <v>22</v>
+      </c>
+      <c r="AR13" t="n">
+        <v>10</v>
+      </c>
+      <c r="AS13" t="n">
+        <v>24</v>
+      </c>
+      <c r="AT13" t="n">
+        <v>16</v>
+      </c>
+      <c r="AU13" t="n">
+        <v>24</v>
+      </c>
+      <c r="AV13" t="n">
+        <v>19</v>
+      </c>
+      <c r="AW13" t="n">
         <v>20</v>
-      </c>
-      <c r="AR13" t="n">
-        <v>11</v>
-      </c>
-      <c r="AS13" t="n">
-        <v>23</v>
-      </c>
-      <c r="AT13" t="n">
-        <v>18</v>
-      </c>
-      <c r="AU13" t="n">
-        <v>22</v>
-      </c>
-      <c r="AV13" t="n">
-        <v>21</v>
-      </c>
-      <c r="AW13" t="n">
-        <v>19</v>
       </c>
       <c r="AX13" t="n">
         <v>2</v>
       </c>
       <c r="AY13" t="n">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="AZ13" t="n">
         <v>18</v>
@@ -2813,7 +2880,7 @@
         <v>26</v>
       </c>
       <c r="BB13" t="n">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="BC13" t="n">
         <v>29</v>
@@ -2828,7 +2895,7 @@
       </c>
       <c r="BF13" t="inlineStr">
         <is>
-          <t>2-2-2008-09</t>
+          <t>2009-02-02</t>
         </is>
       </c>
     </row>
@@ -2860,49 +2927,49 @@
         <v>48.2</v>
       </c>
       <c r="I14" t="n">
-        <v>40.3</v>
+        <v>40.1</v>
       </c>
       <c r="J14" t="n">
-        <v>84.09999999999999</v>
+        <v>84</v>
       </c>
       <c r="K14" t="n">
-        <v>0.479</v>
+        <v>0.478</v>
       </c>
       <c r="L14" t="n">
         <v>7.1</v>
       </c>
       <c r="M14" t="n">
-        <v>18.9</v>
+        <v>18.7</v>
       </c>
       <c r="N14" t="n">
-        <v>0.374</v>
+        <v>0.377</v>
       </c>
       <c r="O14" t="n">
-        <v>21.4</v>
+        <v>21</v>
       </c>
       <c r="P14" t="n">
-        <v>27.7</v>
+        <v>27.3</v>
       </c>
       <c r="Q14" t="n">
-        <v>0.773</v>
+        <v>0.771</v>
       </c>
       <c r="R14" t="n">
-        <v>12.4</v>
+        <v>12.3</v>
       </c>
       <c r="S14" t="n">
-        <v>31.6</v>
+        <v>31.7</v>
       </c>
       <c r="T14" t="n">
         <v>44</v>
       </c>
       <c r="U14" t="n">
-        <v>23.3</v>
+        <v>23.2</v>
       </c>
       <c r="V14" t="n">
         <v>13.8</v>
       </c>
       <c r="W14" t="n">
-        <v>8.300000000000001</v>
+        <v>8.4</v>
       </c>
       <c r="X14" t="n">
         <v>5.3</v>
@@ -2911,37 +2978,37 @@
         <v>4.3</v>
       </c>
       <c r="Z14" t="n">
-        <v>20.2</v>
+        <v>20.1</v>
       </c>
       <c r="AA14" t="n">
-        <v>23</v>
+        <v>22.7</v>
       </c>
       <c r="AB14" t="n">
-        <v>109</v>
+        <v>108.3</v>
       </c>
       <c r="AC14" t="n">
-        <v>8.5</v>
+        <v>8.800000000000001</v>
       </c>
       <c r="AD14" t="n">
-        <v>23</v>
+        <v>17</v>
       </c>
       <c r="AE14" t="n">
         <v>2</v>
       </c>
       <c r="AF14" t="n">
+        <v>1</v>
+      </c>
+      <c r="AG14" t="n">
         <v>2</v>
       </c>
-      <c r="AG14" t="n">
-        <v>3</v>
-      </c>
       <c r="AH14" t="n">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="AI14" t="n">
         <v>1</v>
       </c>
       <c r="AJ14" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="AK14" t="n">
         <v>3</v>
@@ -2953,7 +3020,7 @@
         <v>13</v>
       </c>
       <c r="AN14" t="n">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="AO14" t="n">
         <v>4</v>
@@ -2965,7 +3032,7 @@
         <v>12</v>
       </c>
       <c r="AR14" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="AS14" t="n">
         <v>8</v>
@@ -2992,7 +3059,7 @@
         <v>7</v>
       </c>
       <c r="BA14" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="BB14" t="n">
         <v>1</v>
@@ -3010,7 +3077,7 @@
       </c>
       <c r="BF14" t="inlineStr">
         <is>
-          <t>2-2-2008-09</t>
+          <t>2009-02-02</t>
         </is>
       </c>
     </row>
@@ -3027,46 +3094,46 @@
         </is>
       </c>
       <c r="D15" t="n">
-        <v>47</v>
+        <v>46</v>
       </c>
       <c r="E15" t="n">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="F15" t="n">
         <v>35</v>
       </c>
       <c r="G15" t="n">
-        <v>0.255</v>
+        <v>0.239</v>
       </c>
       <c r="H15" t="n">
         <v>48.5</v>
       </c>
       <c r="I15" t="n">
-        <v>34.7</v>
+        <v>34.5</v>
       </c>
       <c r="J15" t="n">
-        <v>77.2</v>
+        <v>77.09999999999999</v>
       </c>
       <c r="K15" t="n">
-        <v>0.449</v>
+        <v>0.448</v>
       </c>
       <c r="L15" t="n">
-        <v>4.6</v>
+        <v>4.5</v>
       </c>
       <c r="M15" t="n">
         <v>13.6</v>
       </c>
       <c r="N15" t="n">
-        <v>0.336</v>
+        <v>0.332</v>
       </c>
       <c r="O15" t="n">
-        <v>19.4</v>
+        <v>19.3</v>
       </c>
       <c r="P15" t="n">
-        <v>25.8</v>
+        <v>25.7</v>
       </c>
       <c r="Q15" t="n">
-        <v>0.753</v>
+        <v>0.752</v>
       </c>
       <c r="R15" t="n">
         <v>10.1</v>
@@ -3078,16 +3145,16 @@
         <v>38.1</v>
       </c>
       <c r="U15" t="n">
-        <v>16.7</v>
+        <v>16.6</v>
       </c>
       <c r="V15" t="n">
-        <v>14.9</v>
+        <v>15</v>
       </c>
       <c r="W15" t="n">
-        <v>7.8</v>
+        <v>7.7</v>
       </c>
       <c r="X15" t="n">
-        <v>4.1</v>
+        <v>4.2</v>
       </c>
       <c r="Y15" t="n">
         <v>5.2</v>
@@ -3096,16 +3163,16 @@
         <v>22</v>
       </c>
       <c r="AA15" t="n">
-        <v>21.9</v>
+        <v>21.7</v>
       </c>
       <c r="AB15" t="n">
-        <v>93.3</v>
+        <v>92.90000000000001</v>
       </c>
       <c r="AC15" t="n">
-        <v>-6.7</v>
+        <v>-7.2</v>
       </c>
       <c r="AD15" t="n">
-        <v>14</v>
+        <v>17</v>
       </c>
       <c r="AE15" t="n">
         <v>26</v>
@@ -3117,7 +3184,7 @@
         <v>26</v>
       </c>
       <c r="AH15" t="n">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="AI15" t="n">
         <v>29</v>
@@ -3126,7 +3193,7 @@
         <v>27</v>
       </c>
       <c r="AK15" t="n">
-        <v>19</v>
+        <v>21</v>
       </c>
       <c r="AL15" t="n">
         <v>27</v>
@@ -3135,10 +3202,10 @@
         <v>27</v>
       </c>
       <c r="AN15" t="n">
-        <v>27</v>
+        <v>28</v>
       </c>
       <c r="AO15" t="n">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="AP15" t="n">
         <v>9</v>
@@ -3159,28 +3226,28 @@
         <v>30</v>
       </c>
       <c r="AV15" t="n">
+        <v>20</v>
+      </c>
+      <c r="AW15" t="n">
+        <v>9</v>
+      </c>
+      <c r="AX15" t="n">
+        <v>24</v>
+      </c>
+      <c r="AY15" t="n">
         <v>17</v>
       </c>
-      <c r="AW15" t="n">
-        <v>8</v>
-      </c>
-      <c r="AX15" t="n">
-        <v>25</v>
-      </c>
-      <c r="AY15" t="n">
-        <v>18</v>
-      </c>
       <c r="AZ15" t="n">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="BA15" t="n">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="BB15" t="n">
-        <v>27</v>
+        <v>29</v>
       </c>
       <c r="BC15" t="n">
-        <v>27</v>
+        <v>28</v>
       </c>
       <c r="BD15" t="n">
         <v>10</v>
@@ -3192,7 +3259,7 @@
       </c>
       <c r="BF15" t="inlineStr">
         <is>
-          <t>2-2-2008-09</t>
+          <t>2009-02-02</t>
         </is>
       </c>
     </row>
@@ -3209,58 +3276,58 @@
         </is>
       </c>
       <c r="D16" t="n">
-        <v>47</v>
+        <v>46</v>
       </c>
       <c r="E16" t="n">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="F16" t="n">
         <v>21</v>
       </c>
       <c r="G16" t="n">
-        <v>0.553</v>
+        <v>0.543</v>
       </c>
       <c r="H16" t="n">
         <v>48.3</v>
       </c>
       <c r="I16" t="n">
-        <v>36.4</v>
+        <v>36.2</v>
       </c>
       <c r="J16" t="n">
         <v>80.90000000000001</v>
       </c>
       <c r="K16" t="n">
-        <v>0.449</v>
+        <v>0.447</v>
       </c>
       <c r="L16" t="n">
         <v>7</v>
       </c>
       <c r="M16" t="n">
-        <v>19.6</v>
+        <v>19.7</v>
       </c>
       <c r="N16" t="n">
-        <v>0.358</v>
+        <v>0.354</v>
       </c>
       <c r="O16" t="n">
-        <v>17.3</v>
+        <v>17.2</v>
       </c>
       <c r="P16" t="n">
-        <v>23.3</v>
+        <v>23.2</v>
       </c>
       <c r="Q16" t="n">
-        <v>0.743</v>
+        <v>0.742</v>
       </c>
       <c r="R16" t="n">
-        <v>10.4</v>
+        <v>10.3</v>
       </c>
       <c r="S16" t="n">
-        <v>29.6</v>
+        <v>29.5</v>
       </c>
       <c r="T16" t="n">
         <v>39.9</v>
       </c>
       <c r="U16" t="n">
-        <v>19.8</v>
+        <v>19.6</v>
       </c>
       <c r="V16" t="n">
         <v>12.6</v>
@@ -3275,19 +3342,19 @@
         <v>4.2</v>
       </c>
       <c r="Z16" t="n">
-        <v>20.5</v>
+        <v>20.6</v>
       </c>
       <c r="AA16" t="n">
         <v>19.8</v>
       </c>
       <c r="AB16" t="n">
-        <v>97</v>
+        <v>96.5</v>
       </c>
       <c r="AC16" t="n">
-        <v>0.7</v>
+        <v>0.2</v>
       </c>
       <c r="AD16" t="n">
-        <v>14</v>
+        <v>17</v>
       </c>
       <c r="AE16" t="n">
         <v>13</v>
@@ -3299,16 +3366,16 @@
         <v>13</v>
       </c>
       <c r="AH16" t="n">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="AI16" t="n">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="AJ16" t="n">
         <v>13</v>
       </c>
       <c r="AK16" t="n">
-        <v>18</v>
+        <v>22</v>
       </c>
       <c r="AL16" t="n">
         <v>12</v>
@@ -3317,16 +3384,16 @@
         <v>10</v>
       </c>
       <c r="AN16" t="n">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="AO16" t="n">
         <v>26</v>
       </c>
       <c r="AP16" t="n">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="AQ16" t="n">
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="AR16" t="n">
         <v>24</v>
@@ -3335,7 +3402,7 @@
         <v>20</v>
       </c>
       <c r="AT16" t="n">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="AU16" t="n">
         <v>26</v>
@@ -3347,7 +3414,7 @@
         <v>5</v>
       </c>
       <c r="AX16" t="n">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="AY16" t="n">
         <v>9</v>
@@ -3359,10 +3426,10 @@
         <v>25</v>
       </c>
       <c r="BB16" t="n">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="BC16" t="n">
-        <v>14</v>
+        <v>16</v>
       </c>
       <c r="BD16" t="n">
         <v>10</v>
@@ -3374,7 +3441,7 @@
       </c>
       <c r="BF16" t="inlineStr">
         <is>
-          <t>2-2-2008-09</t>
+          <t>2009-02-02</t>
         </is>
       </c>
     </row>
@@ -3391,16 +3458,16 @@
         </is>
       </c>
       <c r="D17" t="n">
-        <v>50</v>
+        <v>51</v>
       </c>
       <c r="E17" t="n">
         <v>24</v>
       </c>
       <c r="F17" t="n">
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="G17" t="n">
-        <v>0.48</v>
+        <v>0.471</v>
       </c>
       <c r="H17" t="n">
         <v>48.3</v>
@@ -3409,43 +3476,43 @@
         <v>36.5</v>
       </c>
       <c r="J17" t="n">
-        <v>81.3</v>
+        <v>81.2</v>
       </c>
       <c r="K17" t="n">
-        <v>0.448</v>
+        <v>0.449</v>
       </c>
       <c r="L17" t="n">
         <v>5.6</v>
       </c>
       <c r="M17" t="n">
-        <v>16</v>
+        <v>15.9</v>
       </c>
       <c r="N17" t="n">
-        <v>0.35</v>
+        <v>0.351</v>
       </c>
       <c r="O17" t="n">
-        <v>19.9</v>
+        <v>19.8</v>
       </c>
       <c r="P17" t="n">
-        <v>25.3</v>
+        <v>25.2</v>
       </c>
       <c r="Q17" t="n">
-        <v>0.787</v>
+        <v>0.786</v>
       </c>
       <c r="R17" t="n">
         <v>12.1</v>
       </c>
       <c r="S17" t="n">
-        <v>29.5</v>
+        <v>29.3</v>
       </c>
       <c r="T17" t="n">
-        <v>41.6</v>
+        <v>41.4</v>
       </c>
       <c r="U17" t="n">
         <v>21.3</v>
       </c>
       <c r="V17" t="n">
-        <v>14.5</v>
+        <v>14.6</v>
       </c>
       <c r="W17" t="n">
         <v>7.1</v>
@@ -3457,16 +3524,16 @@
         <v>4.6</v>
       </c>
       <c r="Z17" t="n">
-        <v>23.7</v>
+        <v>23.9</v>
       </c>
       <c r="AA17" t="n">
-        <v>22.7</v>
+        <v>22.6</v>
       </c>
       <c r="AB17" t="n">
-        <v>98.40000000000001</v>
+        <v>98.3</v>
       </c>
       <c r="AC17" t="n">
-        <v>0.4</v>
+        <v>0.2</v>
       </c>
       <c r="AD17" t="n">
         <v>1</v>
@@ -3475,7 +3542,7 @@
         <v>16</v>
       </c>
       <c r="AF17" t="n">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="AG17" t="n">
         <v>17</v>
@@ -3490,7 +3557,7 @@
         <v>12</v>
       </c>
       <c r="AK17" t="n">
-        <v>20</v>
+        <v>18</v>
       </c>
       <c r="AL17" t="n">
         <v>23</v>
@@ -3499,13 +3566,13 @@
         <v>23</v>
       </c>
       <c r="AN17" t="n">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="AO17" t="n">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="AP17" t="n">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="AQ17" t="n">
         <v>9</v>
@@ -3520,7 +3587,7 @@
         <v>14</v>
       </c>
       <c r="AU17" t="n">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="AV17" t="n">
         <v>16</v>
@@ -3532,10 +3599,10 @@
         <v>28</v>
       </c>
       <c r="AY17" t="n">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="AZ17" t="n">
-        <v>28</v>
+        <v>30</v>
       </c>
       <c r="BA17" t="n">
         <v>6</v>
@@ -3544,7 +3611,7 @@
         <v>17</v>
       </c>
       <c r="BC17" t="n">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="BD17" t="n">
         <v>10</v>
@@ -3556,7 +3623,7 @@
       </c>
       <c r="BF17" t="inlineStr">
         <is>
-          <t>2-2-2008-09</t>
+          <t>2009-02-02</t>
         </is>
       </c>
     </row>
@@ -3651,7 +3718,7 @@
         <v>-3.5</v>
       </c>
       <c r="AD18" t="n">
-        <v>23</v>
+        <v>17</v>
       </c>
       <c r="AE18" t="n">
         <v>24</v>
@@ -3711,7 +3778,7 @@
         <v>28</v>
       </c>
       <c r="AX18" t="n">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="AY18" t="n">
         <v>30</v>
@@ -3720,10 +3787,10 @@
         <v>19</v>
       </c>
       <c r="BA18" t="n">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="BB18" t="n">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="BC18" t="n">
         <v>24</v>
@@ -3738,7 +3805,7 @@
       </c>
       <c r="BF18" t="inlineStr">
         <is>
-          <t>2-2-2008-09</t>
+          <t>2009-02-02</t>
         </is>
       </c>
     </row>
@@ -3833,19 +3900,19 @@
         <v>-3.2</v>
       </c>
       <c r="AD19" t="n">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="AE19" t="n">
         <v>18</v>
       </c>
       <c r="AF19" t="n">
-        <v>19</v>
+        <v>18</v>
       </c>
       <c r="AG19" t="n">
         <v>19</v>
       </c>
       <c r="AH19" t="n">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="AI19" t="n">
         <v>26</v>
@@ -3860,19 +3927,19 @@
         <v>6</v>
       </c>
       <c r="AM19" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="AN19" t="n">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="AO19" t="n">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="AP19" t="n">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="AQ19" t="n">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="AR19" t="n">
         <v>14</v>
@@ -3890,13 +3957,13 @@
         <v>10</v>
       </c>
       <c r="AW19" t="n">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="AX19" t="n">
         <v>21</v>
       </c>
       <c r="AY19" t="n">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="AZ19" t="n">
         <v>27</v>
@@ -3920,7 +3987,7 @@
       </c>
       <c r="BF19" t="inlineStr">
         <is>
-          <t>2-2-2008-09</t>
+          <t>2009-02-02</t>
         </is>
       </c>
     </row>
@@ -3937,16 +4004,16 @@
         </is>
       </c>
       <c r="D20" t="n">
-        <v>45</v>
+        <v>44</v>
       </c>
       <c r="E20" t="n">
         <v>28</v>
       </c>
       <c r="F20" t="n">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="G20" t="n">
-        <v>0.622</v>
+        <v>0.636</v>
       </c>
       <c r="H20" t="n">
         <v>48</v>
@@ -3955,25 +4022,25 @@
         <v>35</v>
       </c>
       <c r="J20" t="n">
-        <v>76.5</v>
+        <v>76.40000000000001</v>
       </c>
       <c r="K20" t="n">
-        <v>0.458</v>
+        <v>0.459</v>
       </c>
       <c r="L20" t="n">
-        <v>7.6</v>
+        <v>7.7</v>
       </c>
       <c r="M20" t="n">
         <v>19.5</v>
       </c>
       <c r="N20" t="n">
-        <v>0.39</v>
+        <v>0.392</v>
       </c>
       <c r="O20" t="n">
-        <v>18.2</v>
+        <v>18.3</v>
       </c>
       <c r="P20" t="n">
-        <v>22.5</v>
+        <v>22.6</v>
       </c>
       <c r="Q20" t="n">
         <v>0.8090000000000001</v>
@@ -3982,19 +4049,19 @@
         <v>9.5</v>
       </c>
       <c r="S20" t="n">
-        <v>29</v>
+        <v>29.2</v>
       </c>
       <c r="T20" t="n">
-        <v>38.5</v>
+        <v>38.6</v>
       </c>
       <c r="U20" t="n">
-        <v>19.7</v>
+        <v>19.6</v>
       </c>
       <c r="V20" t="n">
-        <v>12.7</v>
+        <v>12.8</v>
       </c>
       <c r="W20" t="n">
-        <v>7.6</v>
+        <v>7.5</v>
       </c>
       <c r="X20" t="n">
         <v>4.3</v>
@@ -4009,34 +4076,34 @@
         <v>21</v>
       </c>
       <c r="AB20" t="n">
-        <v>95.90000000000001</v>
+        <v>96</v>
       </c>
       <c r="AC20" t="n">
-        <v>2.8</v>
+        <v>3.1</v>
       </c>
       <c r="AD20" t="n">
-        <v>29</v>
+        <v>30</v>
       </c>
       <c r="AE20" t="n">
         <v>9</v>
       </c>
       <c r="AF20" t="n">
-        <v>8</v>
+        <v>6</v>
       </c>
       <c r="AG20" t="n">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="AH20" t="n">
         <v>30</v>
       </c>
       <c r="AI20" t="n">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="AJ20" t="n">
         <v>29</v>
       </c>
       <c r="AK20" t="n">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="AL20" t="n">
         <v>7</v>
@@ -4045,22 +4112,22 @@
         <v>11</v>
       </c>
       <c r="AN20" t="n">
+        <v>3</v>
+      </c>
+      <c r="AO20" t="n">
+        <v>23</v>
+      </c>
+      <c r="AP20" t="n">
+        <v>26</v>
+      </c>
+      <c r="AQ20" t="n">
         <v>4</v>
       </c>
-      <c r="AO20" t="n">
-        <v>24</v>
-      </c>
-      <c r="AP20" t="n">
+      <c r="AR20" t="n">
         <v>27</v>
       </c>
-      <c r="AQ20" t="n">
-        <v>3</v>
-      </c>
-      <c r="AR20" t="n">
-        <v>28</v>
-      </c>
       <c r="AS20" t="n">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="AT20" t="n">
         <v>29</v>
@@ -4072,7 +4139,7 @@
         <v>4</v>
       </c>
       <c r="AW20" t="n">
-        <v>10</v>
+        <v>12</v>
       </c>
       <c r="AX20" t="n">
         <v>22</v>
@@ -4090,7 +4157,7 @@
         <v>25</v>
       </c>
       <c r="BC20" t="n">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="BD20" t="n">
         <v>10</v>
@@ -4102,7 +4169,7 @@
       </c>
       <c r="BF20" t="inlineStr">
         <is>
-          <t>2-2-2008-09</t>
+          <t>2009-02-02</t>
         </is>
       </c>
     </row>
@@ -4119,52 +4186,52 @@
         </is>
       </c>
       <c r="D21" t="n">
-        <v>47</v>
+        <v>46</v>
       </c>
       <c r="E21" t="n">
         <v>21</v>
       </c>
       <c r="F21" t="n">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="G21" t="n">
-        <v>0.447</v>
+        <v>0.457</v>
       </c>
       <c r="H21" t="n">
         <v>48.1</v>
       </c>
       <c r="I21" t="n">
-        <v>37.9</v>
+        <v>37.8</v>
       </c>
       <c r="J21" t="n">
-        <v>86</v>
+        <v>85.90000000000001</v>
       </c>
       <c r="K21" t="n">
         <v>0.441</v>
       </c>
       <c r="L21" t="n">
-        <v>10.3</v>
+        <v>10.4</v>
       </c>
       <c r="M21" t="n">
         <v>28.9</v>
       </c>
       <c r="N21" t="n">
-        <v>0.357</v>
+        <v>0.359</v>
       </c>
       <c r="O21" t="n">
-        <v>18.3</v>
+        <v>18</v>
       </c>
       <c r="P21" t="n">
-        <v>22.8</v>
+        <v>22.6</v>
       </c>
       <c r="Q21" t="n">
-        <v>0.8</v>
+        <v>0.799</v>
       </c>
       <c r="R21" t="n">
-        <v>11</v>
+        <v>10.9</v>
       </c>
       <c r="S21" t="n">
-        <v>31.6</v>
+        <v>31.7</v>
       </c>
       <c r="T21" t="n">
         <v>42.6</v>
@@ -4182,22 +4249,22 @@
         <v>2.5</v>
       </c>
       <c r="Y21" t="n">
-        <v>5.3</v>
+        <v>5.2</v>
       </c>
       <c r="Z21" t="n">
-        <v>20.2</v>
+        <v>20</v>
       </c>
       <c r="AA21" t="n">
-        <v>19.1</v>
+        <v>19</v>
       </c>
       <c r="AB21" t="n">
-        <v>104.3</v>
+        <v>104.1</v>
       </c>
       <c r="AC21" t="n">
-        <v>-2.1</v>
+        <v>-2</v>
       </c>
       <c r="AD21" t="n">
-        <v>14</v>
+        <v>17</v>
       </c>
       <c r="AE21" t="n">
         <v>18</v>
@@ -4209,7 +4276,7 @@
         <v>18</v>
       </c>
       <c r="AH21" t="n">
-        <v>26</v>
+        <v>24</v>
       </c>
       <c r="AI21" t="n">
         <v>7</v>
@@ -4227,22 +4294,22 @@
         <v>1</v>
       </c>
       <c r="AN21" t="n">
-        <v>20</v>
+        <v>18</v>
       </c>
       <c r="AO21" t="n">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="AP21" t="n">
-        <v>24</v>
+        <v>27</v>
       </c>
       <c r="AQ21" t="n">
         <v>7</v>
       </c>
       <c r="AR21" t="n">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="AS21" t="n">
-        <v>9</v>
+        <v>5</v>
       </c>
       <c r="AT21" t="n">
         <v>9</v>
@@ -4260,10 +4327,10 @@
         <v>30</v>
       </c>
       <c r="AY21" t="n">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="AZ21" t="n">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="BA21" t="n">
         <v>29</v>
@@ -4284,7 +4351,7 @@
       </c>
       <c r="BF21" t="inlineStr">
         <is>
-          <t>2-2-2008-09</t>
+          <t>2009-02-02</t>
         </is>
       </c>
     </row>
@@ -4379,10 +4446,10 @@
         <v>-6.2</v>
       </c>
       <c r="AD22" t="n">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="AE22" t="n">
-        <v>27</v>
+        <v>26</v>
       </c>
       <c r="AF22" t="n">
         <v>27</v>
@@ -4397,10 +4464,10 @@
         <v>16</v>
       </c>
       <c r="AJ22" t="n">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="AK22" t="n">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="AL22" t="n">
         <v>30</v>
@@ -4409,10 +4476,10 @@
         <v>30</v>
       </c>
       <c r="AN22" t="n">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="AO22" t="n">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="AP22" t="n">
         <v>8</v>
@@ -4427,7 +4494,7 @@
         <v>11</v>
       </c>
       <c r="AT22" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="AU22" t="n">
         <v>23</v>
@@ -4445,13 +4512,13 @@
         <v>22</v>
       </c>
       <c r="AZ22" t="n">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="BA22" t="n">
         <v>17</v>
       </c>
       <c r="BB22" t="n">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="BC22" t="n">
         <v>26</v>
@@ -4466,7 +4533,7 @@
       </c>
       <c r="BF22" t="inlineStr">
         <is>
-          <t>2-2-2008-09</t>
+          <t>2009-02-02</t>
         </is>
       </c>
     </row>
@@ -4483,16 +4550,16 @@
         </is>
       </c>
       <c r="D23" t="n">
-        <v>47</v>
+        <v>46</v>
       </c>
       <c r="E23" t="n">
         <v>36</v>
       </c>
       <c r="F23" t="n">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="G23" t="n">
-        <v>0.766</v>
+        <v>0.783</v>
       </c>
       <c r="H23" t="n">
         <v>48.1</v>
@@ -4501,49 +4568,49 @@
         <v>36.3</v>
       </c>
       <c r="J23" t="n">
-        <v>78.7</v>
+        <v>78.59999999999999</v>
       </c>
       <c r="K23" t="n">
-        <v>0.461</v>
+        <v>0.462</v>
       </c>
       <c r="L23" t="n">
-        <v>10.4</v>
+        <v>10.5</v>
       </c>
       <c r="M23" t="n">
-        <v>26.1</v>
+        <v>26.3</v>
       </c>
       <c r="N23" t="n">
-        <v>0.397</v>
+        <v>0.401</v>
       </c>
       <c r="O23" t="n">
         <v>19.5</v>
       </c>
       <c r="P23" t="n">
-        <v>26.9</v>
+        <v>26.8</v>
       </c>
       <c r="Q23" t="n">
-        <v>0.727</v>
+        <v>0.726</v>
       </c>
       <c r="R23" t="n">
         <v>10</v>
       </c>
       <c r="S23" t="n">
-        <v>33</v>
+        <v>33.1</v>
       </c>
       <c r="T23" t="n">
-        <v>43</v>
+        <v>43.1</v>
       </c>
       <c r="U23" t="n">
-        <v>19.4</v>
+        <v>19.5</v>
       </c>
       <c r="V23" t="n">
-        <v>13.9</v>
+        <v>14</v>
       </c>
       <c r="W23" t="n">
         <v>7.2</v>
       </c>
       <c r="X23" t="n">
-        <v>5.4</v>
+        <v>5.5</v>
       </c>
       <c r="Y23" t="n">
         <v>3.7</v>
@@ -4552,16 +4619,16 @@
         <v>20</v>
       </c>
       <c r="AA23" t="n">
-        <v>22.1</v>
+        <v>22</v>
       </c>
       <c r="AB23" t="n">
-        <v>102.4</v>
+        <v>102.6</v>
       </c>
       <c r="AC23" t="n">
-        <v>8.1</v>
+        <v>8.5</v>
       </c>
       <c r="AD23" t="n">
-        <v>14</v>
+        <v>17</v>
       </c>
       <c r="AE23" t="n">
         <v>4</v>
@@ -4573,16 +4640,16 @@
         <v>4</v>
       </c>
       <c r="AH23" t="n">
-        <v>26</v>
+        <v>24</v>
       </c>
       <c r="AI23" t="n">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="AJ23" t="n">
         <v>21</v>
       </c>
       <c r="AK23" t="n">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="AL23" t="n">
         <v>1</v>
@@ -4594,7 +4661,7 @@
         <v>1</v>
       </c>
       <c r="AO23" t="n">
-        <v>10</v>
+        <v>12</v>
       </c>
       <c r="AP23" t="n">
         <v>6</v>
@@ -4609,7 +4676,7 @@
         <v>1</v>
       </c>
       <c r="AT23" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="AU23" t="n">
         <v>28</v>
@@ -4648,7 +4715,7 @@
       </c>
       <c r="BF23" t="inlineStr">
         <is>
-          <t>2-2-2008-09</t>
+          <t>2009-02-02</t>
         </is>
       </c>
     </row>
@@ -4743,7 +4810,7 @@
         <v>0.6</v>
       </c>
       <c r="AD24" t="n">
-        <v>23</v>
+        <v>17</v>
       </c>
       <c r="AE24" t="n">
         <v>17</v>
@@ -4755,16 +4822,16 @@
         <v>16</v>
       </c>
       <c r="AH24" t="n">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="AI24" t="n">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="AJ24" t="n">
         <v>15</v>
       </c>
       <c r="AK24" t="n">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="AL24" t="n">
         <v>29</v>
@@ -4776,10 +4843,10 @@
         <v>29</v>
       </c>
       <c r="AO24" t="n">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="AP24" t="n">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="AQ24" t="n">
         <v>29</v>
@@ -4791,19 +4858,19 @@
         <v>16</v>
       </c>
       <c r="AT24" t="n">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="AU24" t="n">
         <v>15</v>
       </c>
       <c r="AV24" t="n">
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="AW24" t="n">
         <v>6</v>
       </c>
       <c r="AX24" t="n">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="AY24" t="n">
         <v>15</v>
@@ -4818,7 +4885,7 @@
         <v>24</v>
       </c>
       <c r="BC24" t="n">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="BD24" t="n">
         <v>10</v>
@@ -4830,7 +4897,7 @@
       </c>
       <c r="BF24" t="inlineStr">
         <is>
-          <t>2-2-2008-09</t>
+          <t>2009-02-02</t>
         </is>
       </c>
     </row>
@@ -4847,55 +4914,55 @@
         </is>
       </c>
       <c r="D25" t="n">
-        <v>46</v>
+        <v>45</v>
       </c>
       <c r="E25" t="n">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="F25" t="n">
         <v>20</v>
       </c>
       <c r="G25" t="n">
-        <v>0.5649999999999999</v>
+        <v>0.556</v>
       </c>
       <c r="H25" t="n">
         <v>48.2</v>
       </c>
       <c r="I25" t="n">
-        <v>38.5</v>
+        <v>38.4</v>
       </c>
       <c r="J25" t="n">
-        <v>77.5</v>
+        <v>77.3</v>
       </c>
       <c r="K25" t="n">
         <v>0.496</v>
       </c>
       <c r="L25" t="n">
-        <v>6.5</v>
+        <v>6.6</v>
       </c>
       <c r="M25" t="n">
-        <v>16.9</v>
+        <v>17</v>
       </c>
       <c r="N25" t="n">
-        <v>0.387</v>
+        <v>0.386</v>
       </c>
       <c r="O25" t="n">
-        <v>21</v>
+        <v>20.7</v>
       </c>
       <c r="P25" t="n">
-        <v>27.5</v>
+        <v>27.2</v>
       </c>
       <c r="Q25" t="n">
-        <v>0.763</v>
+        <v>0.761</v>
       </c>
       <c r="R25" t="n">
-        <v>9.699999999999999</v>
+        <v>9.4</v>
       </c>
       <c r="S25" t="n">
-        <v>31.8</v>
+        <v>31.7</v>
       </c>
       <c r="T25" t="n">
-        <v>41.5</v>
+        <v>41.1</v>
       </c>
       <c r="U25" t="n">
         <v>21.8</v>
@@ -4904,7 +4971,7 @@
         <v>16.3</v>
       </c>
       <c r="W25" t="n">
-        <v>6.3</v>
+        <v>6.1</v>
       </c>
       <c r="X25" t="n">
         <v>5</v>
@@ -4916,16 +4983,16 @@
         <v>20.4</v>
       </c>
       <c r="AA25" t="n">
-        <v>22.6</v>
+        <v>22.4</v>
       </c>
       <c r="AB25" t="n">
-        <v>104.5</v>
+        <v>104</v>
       </c>
       <c r="AC25" t="n">
-        <v>1.6</v>
+        <v>0.6</v>
       </c>
       <c r="AD25" t="n">
-        <v>23</v>
+        <v>29</v>
       </c>
       <c r="AE25" t="n">
         <v>13</v>
@@ -4958,19 +5025,19 @@
         <v>5</v>
       </c>
       <c r="AO25" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="AP25" t="n">
         <v>5</v>
       </c>
       <c r="AQ25" t="n">
-        <v>19</v>
+        <v>18</v>
       </c>
       <c r="AR25" t="n">
-        <v>27</v>
+        <v>28</v>
       </c>
       <c r="AS25" t="n">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="AT25" t="n">
         <v>15</v>
@@ -4988,7 +5055,7 @@
         <v>12</v>
       </c>
       <c r="AY25" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="AZ25" t="n">
         <v>11</v>
@@ -4997,10 +5064,10 @@
         <v>7</v>
       </c>
       <c r="BB25" t="n">
-        <v>4</v>
+        <v>6</v>
       </c>
       <c r="BC25" t="n">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="BD25" t="n">
         <v>10</v>
@@ -5012,7 +5079,7 @@
       </c>
       <c r="BF25" t="inlineStr">
         <is>
-          <t>2-2-2008-09</t>
+          <t>2009-02-02</t>
         </is>
       </c>
     </row>
@@ -5032,52 +5099,52 @@
         <v>46</v>
       </c>
       <c r="E26" t="n">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="F26" t="n">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="G26" t="n">
-        <v>0.652</v>
+        <v>0.63</v>
       </c>
       <c r="H26" t="n">
         <v>48.4</v>
       </c>
       <c r="I26" t="n">
-        <v>36.2</v>
+        <v>36</v>
       </c>
       <c r="J26" t="n">
-        <v>78.40000000000001</v>
+        <v>78.5</v>
       </c>
       <c r="K26" t="n">
-        <v>0.462</v>
+        <v>0.459</v>
       </c>
       <c r="L26" t="n">
-        <v>7.3</v>
+        <v>7.4</v>
       </c>
       <c r="M26" t="n">
+        <v>19.5</v>
+      </c>
+      <c r="N26" t="n">
+        <v>0.379</v>
+      </c>
+      <c r="O26" t="n">
         <v>19.3</v>
       </c>
-      <c r="N26" t="n">
-        <v>0.377</v>
-      </c>
-      <c r="O26" t="n">
-        <v>19.5</v>
-      </c>
       <c r="P26" t="n">
-        <v>25.5</v>
+        <v>25.4</v>
       </c>
       <c r="Q26" t="n">
-        <v>0.764</v>
+        <v>0.759</v>
       </c>
       <c r="R26" t="n">
         <v>13.2</v>
       </c>
       <c r="S26" t="n">
-        <v>27.8</v>
+        <v>27.6</v>
       </c>
       <c r="T26" t="n">
-        <v>41</v>
+        <v>40.8</v>
       </c>
       <c r="U26" t="n">
         <v>20.3</v>
@@ -5086,7 +5153,7 @@
         <v>12.8</v>
       </c>
       <c r="W26" t="n">
-        <v>6.9</v>
+        <v>7</v>
       </c>
       <c r="X26" t="n">
         <v>4.9</v>
@@ -5095,40 +5162,40 @@
         <v>3.6</v>
       </c>
       <c r="Z26" t="n">
-        <v>21</v>
+        <v>20.9</v>
       </c>
       <c r="AA26" t="n">
-        <v>21.7</v>
+        <v>21.6</v>
       </c>
       <c r="AB26" t="n">
-        <v>99.2</v>
+        <v>98.7</v>
       </c>
       <c r="AC26" t="n">
-        <v>4.6</v>
+        <v>4</v>
       </c>
       <c r="AD26" t="n">
-        <v>23</v>
+        <v>17</v>
       </c>
       <c r="AE26" t="n">
         <v>7</v>
       </c>
       <c r="AF26" t="n">
-        <v>6</v>
+        <v>8</v>
       </c>
       <c r="AG26" t="n">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="AH26" t="n">
         <v>11</v>
       </c>
       <c r="AI26" t="n">
-        <v>19</v>
+        <v>22</v>
       </c>
       <c r="AJ26" t="n">
-        <v>24</v>
+        <v>22</v>
       </c>
       <c r="AK26" t="n">
-        <v>8</v>
+        <v>11</v>
       </c>
       <c r="AL26" t="n">
         <v>10</v>
@@ -5137,16 +5204,16 @@
         <v>12</v>
       </c>
       <c r="AN26" t="n">
-        <v>8</v>
+        <v>6</v>
       </c>
       <c r="AO26" t="n">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="AP26" t="n">
-        <v>10</v>
+        <v>12</v>
       </c>
       <c r="AQ26" t="n">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="AR26" t="n">
         <v>1</v>
@@ -5155,31 +5222,31 @@
         <v>30</v>
       </c>
       <c r="AT26" t="n">
-        <v>17</v>
+        <v>19</v>
       </c>
       <c r="AU26" t="n">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="AV26" t="n">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="AW26" t="n">
-        <v>21</v>
+        <v>19</v>
       </c>
       <c r="AX26" t="n">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="AY26" t="n">
         <v>2</v>
       </c>
       <c r="AZ26" t="n">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="BA26" t="n">
         <v>11</v>
       </c>
       <c r="BB26" t="n">
-        <v>13</v>
+        <v>16</v>
       </c>
       <c r="BC26" t="n">
         <v>5</v>
@@ -5194,7 +5261,7 @@
       </c>
       <c r="BF26" t="inlineStr">
         <is>
-          <t>2-2-2008-09</t>
+          <t>2009-02-02</t>
         </is>
       </c>
     </row>
@@ -5211,28 +5278,28 @@
         </is>
       </c>
       <c r="D27" t="n">
-        <v>50</v>
+        <v>49</v>
       </c>
       <c r="E27" t="n">
         <v>11</v>
       </c>
       <c r="F27" t="n">
-        <v>39</v>
+        <v>38</v>
       </c>
       <c r="G27" t="n">
-        <v>0.22</v>
+        <v>0.224</v>
       </c>
       <c r="H27" t="n">
         <v>48.7</v>
       </c>
       <c r="I27" t="n">
-        <v>36</v>
+        <v>36.1</v>
       </c>
       <c r="J27" t="n">
         <v>81.3</v>
       </c>
       <c r="K27" t="n">
-        <v>0.443</v>
+        <v>0.445</v>
       </c>
       <c r="L27" t="n">
         <v>6.4</v>
@@ -5244,28 +5311,28 @@
         <v>0.35</v>
       </c>
       <c r="O27" t="n">
-        <v>20.5</v>
+        <v>20.7</v>
       </c>
       <c r="P27" t="n">
-        <v>25.4</v>
+        <v>25.6</v>
       </c>
       <c r="Q27" t="n">
-        <v>0.8080000000000001</v>
+        <v>0.8090000000000001</v>
       </c>
       <c r="R27" t="n">
         <v>10.4</v>
       </c>
       <c r="S27" t="n">
-        <v>28.4</v>
+        <v>28.5</v>
       </c>
       <c r="T27" t="n">
-        <v>38.9</v>
+        <v>39</v>
       </c>
       <c r="U27" t="n">
-        <v>19.9</v>
+        <v>20</v>
       </c>
       <c r="V27" t="n">
-        <v>15.8</v>
+        <v>15.6</v>
       </c>
       <c r="W27" t="n">
         <v>6.7</v>
@@ -5277,22 +5344,22 @@
         <v>5.2</v>
       </c>
       <c r="Z27" t="n">
-        <v>23.9</v>
+        <v>23.8</v>
       </c>
       <c r="AA27" t="n">
         <v>21.9</v>
       </c>
       <c r="AB27" t="n">
-        <v>99</v>
+        <v>99.3</v>
       </c>
       <c r="AC27" t="n">
-        <v>-9.800000000000001</v>
+        <v>-9.1</v>
       </c>
       <c r="AD27" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="AE27" t="n">
-        <v>27</v>
+        <v>26</v>
       </c>
       <c r="AF27" t="n">
         <v>30</v>
@@ -5301,16 +5368,16 @@
         <v>28</v>
       </c>
       <c r="AH27" t="n">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="AI27" t="n">
-        <v>22</v>
+        <v>20</v>
       </c>
       <c r="AJ27" t="n">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="AK27" t="n">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="AL27" t="n">
         <v>18</v>
@@ -5319,31 +5386,31 @@
         <v>14</v>
       </c>
       <c r="AN27" t="n">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="AO27" t="n">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="AP27" t="n">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="AQ27" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="AR27" t="n">
         <v>23</v>
       </c>
       <c r="AS27" t="n">
+        <v>27</v>
+      </c>
+      <c r="AT27" t="n">
+        <v>27</v>
+      </c>
+      <c r="AU27" t="n">
+        <v>22</v>
+      </c>
+      <c r="AV27" t="n">
         <v>26</v>
-      </c>
-      <c r="AT27" t="n">
-        <v>28</v>
-      </c>
-      <c r="AU27" t="n">
-        <v>25</v>
-      </c>
-      <c r="AV27" t="n">
-        <v>27</v>
       </c>
       <c r="AW27" t="n">
         <v>25</v>
@@ -5352,16 +5419,16 @@
         <v>27</v>
       </c>
       <c r="AY27" t="n">
-        <v>19</v>
+        <v>18</v>
       </c>
       <c r="AZ27" t="n">
-        <v>30</v>
+        <v>28</v>
       </c>
       <c r="BA27" t="n">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="BB27" t="n">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="BC27" t="n">
         <v>30</v>
@@ -5376,7 +5443,7 @@
       </c>
       <c r="BF27" t="inlineStr">
         <is>
-          <t>2-2-2008-09</t>
+          <t>2009-02-02</t>
         </is>
       </c>
     </row>
@@ -5393,61 +5460,61 @@
         </is>
       </c>
       <c r="D28" t="n">
-        <v>47</v>
+        <v>46</v>
       </c>
       <c r="E28" t="n">
-        <v>33</v>
+        <v>32</v>
       </c>
       <c r="F28" t="n">
         <v>14</v>
       </c>
       <c r="G28" t="n">
-        <v>0.702</v>
+        <v>0.696</v>
       </c>
       <c r="H28" t="n">
         <v>48.7</v>
       </c>
       <c r="I28" t="n">
-        <v>36.9</v>
+        <v>36.8</v>
       </c>
       <c r="J28" t="n">
-        <v>79.40000000000001</v>
+        <v>79.2</v>
       </c>
       <c r="K28" t="n">
         <v>0.465</v>
       </c>
       <c r="L28" t="n">
-        <v>8</v>
+        <v>8.1</v>
       </c>
       <c r="M28" t="n">
-        <v>20.4</v>
+        <v>20.5</v>
       </c>
       <c r="N28" t="n">
-        <v>0.392</v>
+        <v>0.395</v>
       </c>
       <c r="O28" t="n">
-        <v>15.9</v>
+        <v>15.7</v>
       </c>
       <c r="P28" t="n">
-        <v>20.8</v>
+        <v>20.5</v>
       </c>
       <c r="Q28" t="n">
-        <v>0.765</v>
+        <v>0.766</v>
       </c>
       <c r="R28" t="n">
-        <v>8.699999999999999</v>
+        <v>8.6</v>
       </c>
       <c r="S28" t="n">
-        <v>31.7</v>
+        <v>31.5</v>
       </c>
       <c r="T28" t="n">
-        <v>40.4</v>
+        <v>40.1</v>
       </c>
       <c r="U28" t="n">
-        <v>21.9</v>
+        <v>21.8</v>
       </c>
       <c r="V28" t="n">
-        <v>12.2</v>
+        <v>12</v>
       </c>
       <c r="W28" t="n">
         <v>5.8</v>
@@ -5456,22 +5523,22 @@
         <v>4.2</v>
       </c>
       <c r="Y28" t="n">
-        <v>4.2</v>
+        <v>4.1</v>
       </c>
       <c r="Z28" t="n">
-        <v>18.6</v>
+        <v>18.5</v>
       </c>
       <c r="AA28" t="n">
-        <v>19</v>
+        <v>18.8</v>
       </c>
       <c r="AB28" t="n">
-        <v>97.59999999999999</v>
+        <v>97.40000000000001</v>
       </c>
       <c r="AC28" t="n">
         <v>3.3</v>
       </c>
       <c r="AD28" t="n">
-        <v>14</v>
+        <v>17</v>
       </c>
       <c r="AE28" t="n">
         <v>5</v>
@@ -5483,10 +5550,10 @@
         <v>5</v>
       </c>
       <c r="AH28" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="AI28" t="n">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="AJ28" t="n">
         <v>18</v>
@@ -5510,16 +5577,16 @@
         <v>30</v>
       </c>
       <c r="AQ28" t="n">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="AR28" t="n">
         <v>30</v>
       </c>
       <c r="AS28" t="n">
-        <v>7</v>
+        <v>9</v>
       </c>
       <c r="AT28" t="n">
-        <v>21</v>
+        <v>23</v>
       </c>
       <c r="AU28" t="n">
         <v>6</v>
@@ -5531,10 +5598,10 @@
         <v>30</v>
       </c>
       <c r="AX28" t="n">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="AY28" t="n">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="AZ28" t="n">
         <v>1</v>
@@ -5543,7 +5610,7 @@
         <v>30</v>
       </c>
       <c r="BB28" t="n">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="BC28" t="n">
         <v>7</v>
@@ -5558,7 +5625,7 @@
       </c>
       <c r="BF28" t="inlineStr">
         <is>
-          <t>2-2-2008-09</t>
+          <t>2009-02-02</t>
         </is>
       </c>
     </row>
@@ -5653,7 +5720,7 @@
         <v>-2.5</v>
       </c>
       <c r="AD29" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="AE29" t="n">
         <v>21</v>
@@ -5671,10 +5738,10 @@
         <v>21</v>
       </c>
       <c r="AJ29" t="n">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="AK29" t="n">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="AL29" t="n">
         <v>19</v>
@@ -5725,7 +5792,7 @@
         <v>18</v>
       </c>
       <c r="BB29" t="n">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="BC29" t="n">
         <v>22</v>
@@ -5740,7 +5807,7 @@
       </c>
       <c r="BF29" t="inlineStr">
         <is>
-          <t>2-2-2008-09</t>
+          <t>2009-02-02</t>
         </is>
       </c>
     </row>
@@ -5757,16 +5824,16 @@
         </is>
       </c>
       <c r="D30" t="n">
-        <v>49</v>
+        <v>48</v>
       </c>
       <c r="E30" t="n">
-        <v>27</v>
+        <v>26</v>
       </c>
       <c r="F30" t="n">
         <v>22</v>
       </c>
       <c r="G30" t="n">
-        <v>0.551</v>
+        <v>0.542</v>
       </c>
       <c r="H30" t="n">
         <v>48.4</v>
@@ -5775,37 +5842,37 @@
         <v>38</v>
       </c>
       <c r="J30" t="n">
-        <v>79.90000000000001</v>
+        <v>80</v>
       </c>
       <c r="K30" t="n">
-        <v>0.476</v>
+        <v>0.475</v>
       </c>
       <c r="L30" t="n">
         <v>4.6</v>
       </c>
       <c r="M30" t="n">
-        <v>13.7</v>
+        <v>13.8</v>
       </c>
       <c r="N30" t="n">
-        <v>0.337</v>
+        <v>0.336</v>
       </c>
       <c r="O30" t="n">
-        <v>21.4</v>
+        <v>21.3</v>
       </c>
       <c r="P30" t="n">
-        <v>28</v>
+        <v>27.8</v>
       </c>
       <c r="Q30" t="n">
-        <v>0.765</v>
+        <v>0.766</v>
       </c>
       <c r="R30" t="n">
-        <v>11.9</v>
+        <v>12</v>
       </c>
       <c r="S30" t="n">
-        <v>28.9</v>
+        <v>29</v>
       </c>
       <c r="T30" t="n">
-        <v>40.8</v>
+        <v>41</v>
       </c>
       <c r="U30" t="n">
         <v>24.7</v>
@@ -5814,40 +5881,40 @@
         <v>15</v>
       </c>
       <c r="W30" t="n">
-        <v>8.800000000000001</v>
+        <v>8.699999999999999</v>
       </c>
       <c r="X30" t="n">
         <v>4.8</v>
       </c>
       <c r="Y30" t="n">
-        <v>4.9</v>
+        <v>4.8</v>
       </c>
       <c r="Z30" t="n">
-        <v>22.4</v>
+        <v>22.5</v>
       </c>
       <c r="AA30" t="n">
-        <v>23.7</v>
+        <v>23.6</v>
       </c>
       <c r="AB30" t="n">
-        <v>102.1</v>
+        <v>102</v>
       </c>
       <c r="AC30" t="n">
-        <v>2.5</v>
+        <v>2.1</v>
       </c>
       <c r="AD30" t="n">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="AE30" t="n">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="AF30" t="n">
         <v>15</v>
       </c>
       <c r="AG30" t="n">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="AH30" t="n">
-        <v>14</v>
+        <v>12</v>
       </c>
       <c r="AI30" t="n">
         <v>5</v>
@@ -5874,7 +5941,7 @@
         <v>3</v>
       </c>
       <c r="AQ30" t="n">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="AR30" t="n">
         <v>8</v>
@@ -5883,13 +5950,13 @@
         <v>25</v>
       </c>
       <c r="AT30" t="n">
-        <v>19</v>
+        <v>18</v>
       </c>
       <c r="AU30" t="n">
         <v>1</v>
       </c>
       <c r="AV30" t="n">
-        <v>20</v>
+        <v>18</v>
       </c>
       <c r="AW30" t="n">
         <v>2</v>
@@ -5922,7 +5989,7 @@
       </c>
       <c r="BF30" t="inlineStr">
         <is>
-          <t>2-2-2008-09</t>
+          <t>2009-02-02</t>
         </is>
       </c>
     </row>
@@ -5939,22 +6006,22 @@
         </is>
       </c>
       <c r="D31" t="n">
-        <v>48</v>
+        <v>47</v>
       </c>
       <c r="E31" t="n">
         <v>10</v>
       </c>
       <c r="F31" t="n">
-        <v>38</v>
+        <v>37</v>
       </c>
       <c r="G31" t="n">
-        <v>0.208</v>
+        <v>0.213</v>
       </c>
       <c r="H31" t="n">
         <v>48.1</v>
       </c>
       <c r="I31" t="n">
-        <v>36.2</v>
+        <v>36.1</v>
       </c>
       <c r="J31" t="n">
         <v>81.5</v>
@@ -5972,40 +6039,40 @@
         <v>0.322</v>
       </c>
       <c r="O31" t="n">
-        <v>16.8</v>
+        <v>16.7</v>
       </c>
       <c r="P31" t="n">
-        <v>22.2</v>
+        <v>22.1</v>
       </c>
       <c r="Q31" t="n">
-        <v>0.755</v>
+        <v>0.757</v>
       </c>
       <c r="R31" t="n">
-        <v>11.9</v>
+        <v>11.7</v>
       </c>
       <c r="S31" t="n">
         <v>28.1</v>
       </c>
       <c r="T31" t="n">
-        <v>40</v>
+        <v>39.8</v>
       </c>
       <c r="U31" t="n">
         <v>20.4</v>
       </c>
       <c r="V31" t="n">
-        <v>13.9</v>
+        <v>13.8</v>
       </c>
       <c r="W31" t="n">
-        <v>7.5</v>
+        <v>7.6</v>
       </c>
       <c r="X31" t="n">
         <v>4</v>
       </c>
       <c r="Y31" t="n">
-        <v>5.1</v>
+        <v>5.2</v>
       </c>
       <c r="Z31" t="n">
-        <v>20.4</v>
+        <v>20.3</v>
       </c>
       <c r="AA31" t="n">
         <v>19.3</v>
@@ -6014,31 +6081,31 @@
         <v>94.09999999999999</v>
       </c>
       <c r="AC31" t="n">
-        <v>-7.2</v>
+        <v>-7</v>
       </c>
       <c r="AD31" t="n">
-        <v>6</v>
+        <v>12</v>
       </c>
       <c r="AE31" t="n">
         <v>29</v>
       </c>
       <c r="AF31" t="n">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="AG31" t="n">
         <v>29</v>
       </c>
       <c r="AH31" t="n">
-        <v>29</v>
+        <v>28</v>
       </c>
       <c r="AI31" t="n">
-        <v>20</v>
+        <v>19</v>
       </c>
       <c r="AJ31" t="n">
         <v>9</v>
       </c>
       <c r="AK31" t="n">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="AL31" t="n">
         <v>25</v>
@@ -6056,16 +6123,16 @@
         <v>28</v>
       </c>
       <c r="AQ31" t="n">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="AR31" t="n">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="AS31" t="n">
         <v>28</v>
       </c>
       <c r="AT31" t="n">
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="AU31" t="n">
         <v>19</v>
@@ -6074,16 +6141,16 @@
         <v>12</v>
       </c>
       <c r="AW31" t="n">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="AX31" t="n">
         <v>26</v>
       </c>
       <c r="AY31" t="n">
-        <v>17</v>
+        <v>19</v>
       </c>
       <c r="AZ31" t="n">
-        <v>12</v>
+        <v>9</v>
       </c>
       <c r="BA31" t="n">
         <v>28</v>
@@ -6092,7 +6159,7 @@
         <v>26</v>
       </c>
       <c r="BC31" t="n">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="BD31" t="n">
         <v>10</v>
@@ -6104,7 +6171,7 @@
       </c>
       <c r="BF31" t="inlineStr">
         <is>
-          <t>2-2-2008-09</t>
+          <t>2009-02-02</t>
         </is>
       </c>
     </row>
